--- a/reports/20260507/Sprint_217_KPMG.xlsx
+++ b/reports/20260507/Sprint_217_KPMG.xlsx
@@ -653,7 +653,7 @@
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** C H A N G E - A P P L I C A N T - S T A T U S ***  ==&gt;  71f8a56b-8315-4c52-8c65-b778366101d3 (PASS)</t>
+Assertions: *** C H A N G E - A P P L I C A N T - S T A T U S ***  ==&gt;  01220cc9-0917-4a55-aab0-41468c01887e (PASS)</t>
         </is>
       </c>
     </row>
